--- a/Listing/MED01S.xlsx
+++ b/Listing/MED01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="410">
   <si>
     <t/>
   </si>
@@ -511,12 +511,6 @@
     <t>FRESH/C MYK/A STRG10</t>
   </si>
   <si>
-    <t>20095234</t>
-  </si>
-  <si>
-    <t>FRSH CR MA KY.PTH 10</t>
-  </si>
-  <si>
     <t>20034536</t>
   </si>
   <si>
@@ -529,12 +523,6 @@
     <t>FRESH/C MYK ANG LV10</t>
   </si>
   <si>
-    <t>20100140</t>
-  </si>
-  <si>
-    <t>FRSH CARE P&amp;R STRG10</t>
-  </si>
-  <si>
     <t>20131218</t>
   </si>
   <si>
@@ -547,12 +535,24 @@
     <t>FCARE SMASH FRUITY</t>
   </si>
   <si>
+    <t>20141438</t>
+  </si>
+  <si>
+    <t>FCARE SMASH SAKURA</t>
+  </si>
+  <si>
     <t>20135134</t>
   </si>
   <si>
     <t>FRS.CR IN+R/ON MTCHA</t>
   </si>
   <si>
+    <t>20141439</t>
+  </si>
+  <si>
+    <t>FCARE VPBLM SAKURA</t>
+  </si>
+  <si>
     <t>20139593</t>
   </si>
   <si>
@@ -571,18 +571,6 @@
     <t>SAFE/C MYK AGN STR10</t>
   </si>
   <si>
-    <t>20036782</t>
-  </si>
-  <si>
-    <t>C/LANG MYK ANG ORI 8</t>
-  </si>
-  <si>
-    <t>20120915</t>
-  </si>
-  <si>
-    <t>V FRESH HOT 8ML</t>
-  </si>
-  <si>
     <t>20134253</t>
   </si>
   <si>
@@ -595,6 +583,12 @@
     <t>SO FRSH EUCLYP2X10ML</t>
   </si>
   <si>
+    <t>20141329</t>
+  </si>
+  <si>
+    <t>SO FRSH CTRUS 2X10ML</t>
+  </si>
+  <si>
     <t>20091326</t>
   </si>
   <si>
@@ -607,6 +601,12 @@
     <t>PLOSSA P&amp;S CITRUS 10</t>
   </si>
   <si>
+    <t>20141330</t>
+  </si>
+  <si>
+    <t>PLOSSA DUAL SRGHAEYO</t>
+  </si>
+  <si>
     <t>10000097</t>
   </si>
   <si>
@@ -1141,6 +1141,18 @@
     <t>C/LANG EKALPT LVN 60</t>
   </si>
   <si>
+    <t>20141441</t>
+  </si>
+  <si>
+    <t>C.LANG MK.BAYI LVD60</t>
+  </si>
+  <si>
+    <t>20141440</t>
+  </si>
+  <si>
+    <t>C.LANG MK BAYI CHM60</t>
+  </si>
+  <si>
     <t>10037405</t>
   </si>
   <si>
@@ -1229,15 +1241,6 @@
   </si>
   <si>
     <t>KONICARE TELON PLS60</t>
-  </si>
-  <si>
-    <t>20106967</t>
-  </si>
-  <si>
-    <t>IDM MNYK KAYU PTH 52</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
 </sst>
 </file>
@@ -1630,13 +1633,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F185"/>
+  <dimension ref="A1:F186"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
@@ -3038,7 +3041,7 @@
         <v>11</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3098,7 +3101,7 @@
         <v>23</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -3238,7 +3241,7 @@
         <v>45</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3258,7 +3261,7 @@
         <v>48</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3298,7 +3301,7 @@
         <v>54</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -5038,7 +5041,7 @@
         <v>35</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -5058,7 +5061,7 @@
         <v>39</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5078,7 +5081,7 @@
         <v>42</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>224</v>
+        <v>61</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5092,13 +5095,13 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5112,13 +5115,13 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>20</v>
+        <v>224</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -5135,7 +5138,7 @@
         <v>29</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>12</v>
@@ -5155,10 +5158,10 @@
         <v>29</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -5175,7 +5178,7 @@
         <v>29</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>12</v>
@@ -5195,10 +5198,10 @@
         <v>29</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5215,10 +5218,10 @@
         <v>29</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5235,10 +5238,10 @@
         <v>29</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -5255,7 +5258,7 @@
         <v>29</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>20</v>
@@ -5275,7 +5278,7 @@
         <v>29</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>20</v>
@@ -5295,10 +5298,10 @@
         <v>29</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -5315,10 +5318,10 @@
         <v>29</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -5332,13 +5335,33 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="E185" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F185" s="1" t="s">
-        <v>20</v>
+      <c r="B186" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
